--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>是不是先记录到当前阶段为止还能成立的情况？</t>
+          <t>一个来源应该是已经处理完前面部分后的结果。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -1166,12 +1166,12 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>是不是先记录到当前阶段为止还能成立的情况？</t>
+          <t>一个来源应该是已经处理完前面部分后的结果。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>当前阶段</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="R4" s="2" t="inlineStr"/>
@@ -1286,7 +1286,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>这一步好像能从前面接过来，可是分支怎么拆我还没想明白。</t>
+          <t>好像和旧值顺序有关，但从大到小还是从小到大我还没想明白。</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -1307,7 +1307,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>这一步好像能从前面接过来，可是分支怎么拆我还没想明白。</t>
+          <t>好像和旧值顺序有关，但从大到小还是从小到大我还没想明白。</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>我是不是该把满足的那一边排除掉？感觉有点反。 边界一换我就乱了。</t>
+          <t>对象是时间段还是选择本身？我感觉关系有点反。 覆盖关系我搞反了。</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>我是不是该把满足的那一边排除掉？感觉有点反。 边界一换我就乱了。</t>
+          <t>对象是时间段还是选择本身？我感觉关系有点反。 覆盖关系我搞反了。</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1568,35 +1568,35 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，什么叫可行性/状态语义？这个词我没太懂。 如果可以的话，能不能先用这题里的一个小对象解释这个词，而不是直接讲完整做法？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>学生：题面编号、循环范围和数组大小总对不上，我不知道该先用哪个最小样例来检查。 我看样例能跟上，但换成自己写就不知道该先确认哪一步。 我现在不知道该先看思路还是先看代码，所以越写越乱。
-AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。
+AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先拿最小样例核对一个边界、初值或变量范围。
 学生：我能说出一点，但还是不知道它怎么落到这题里。
-AI：好，我们就停在这个局部。你先回答一个更小的问题：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+AI：好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，什么叫可行性/状态语义？这个词我没太懂。 如果可以的话，能不能先用这题里的一个小对象解释这个词，而不是直接讲完整做法？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，什么叫</t>
+          <t>我有点懵，这题里</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>是不是先记录到当前阶段为止还能成立的情况？</t>
+          <t>一个来源应该是已经处理完前面部分后的结果。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -2899,12 +2899,12 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>是不是先记录到当前阶段为止还能成立的情况？</t>
+          <t>一个来源应该是已经处理完前面部分后的结果。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>当前阶段</t>
+          <t>来源</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr"/>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>这一步好像能从前面接过来，可是分支怎么拆我还没想明白。</t>
+          <t>好像和旧值顺序有关，但从大到小还是从小到大我还没想明白。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>这一步好像能从前面接过来，可是分支怎么拆我还没想明白。</t>
+          <t>好像和旧值顺序有关，但从大到小还是从小到大我还没想明白。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>我是不是该把满足的那一边排除掉？感觉有点反。 边界一换我就乱了。</t>
+          <t>对象是时间段还是选择本身？我感觉关系有点反。 覆盖关系我搞反了。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>我是不是该把满足的那一边排除掉？感觉有点反。 边界一换我就乱了。</t>
+          <t>对象是时间段还是选择本身？我感觉关系有点反。 覆盖关系我搞反了。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -4591,35 +4591,35 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，什么叫可行性/状态语义？这个词我没太懂。 如果可以的话，能不能先用这题里的一个小对象解释这个词，而不是直接讲完整做法？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>学生：题面编号、循环范围和数组大小总对不上，我不知道该先用哪个最小样例来检查。 我看样例能跟上，但换成自己写就不知道该先确认哪一步。 我现在不知道该先看思路还是先看代码，所以越写越乱。
-AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。
+AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先拿最小样例核对一个边界、初值或变量范围。
 学生：我能说出一点，但还是不知道它怎么落到这题里。
-AI：好，我们就停在这个局部。你先回答一个更小的问题：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+AI：好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，什么叫可行性/状态语义？这个词我没太懂。 如果可以的话，能不能先用这题里的一个小对象解释这个词，而不是直接讲完整做法？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，什么叫</t>
+          <t>我有点懵，这题里</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">

--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -17,13 +17,13 @@
     <sheet name="bucket_policy" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'dialogue_state_review'!$A$2:$AH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bucket_state_representation'!$A$2:$AH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'bucket_transition'!$A$2:$AH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'bucket_boundary_order'!$A$2:$AH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'bucket_modeling'!$A$2:$AH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'bucket_implementation'!$A$2:$AH$2</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'bucket_policy'!$A$2:$AH$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'dialogue_state_review'!$A$2:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'bucket_state_representation'!$A$2:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'bucket_transition'!$A$2:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'bucket_boundary_order'!$A$2:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'bucket_modeling'!$A$2:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'bucket_implementation'!$A$2:$AJ$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'bucket_policy'!$A$2:$AJ$2</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -517,14 +517,28 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>6. Structured review columns use fixed English options for aggregation: case_decision is accept / revise / drop / discuss.</t>
+          <t>6. Prefer filling the bucket sheets; the main sheet is for global browsing. The summary script will aggregate structured review fields from bucket sheets.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>7. This workbook reviews case/source quality only. It is not an AI-response blind review and should not be used to score condition quality.</t>
+          <t>7. Structured review columns use fixed English options for aggregation: case_decision is accept / revise / drop / discuss.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>8. This workbook reviews case/source quality only. It is not an AI-response blind review and should not be used to score condition quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>9. context_ai_reply / prior_ai_scaffold are only for checking whether the student reply follows the previous scaffold, not for judging that AI reply's quality.</t>
         </is>
       </c>
     </row>
@@ -539,7 +553,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH8"/>
+  <dimension ref="A1:AJ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -576,6 +590,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -749,6 +765,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -919,6 +945,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -1043,6 +1079,8 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1211,6 +1249,8 @@
       <c r="AF4" s="2" t="inlineStr"/>
       <c r="AG4" s="2" t="inlineStr"/>
       <c r="AH4" s="2" t="inlineStr"/>
+      <c r="AI4" s="2" t="inlineStr"/>
+      <c r="AJ4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1356,6 +1396,8 @@
       <c r="AF5" s="2" t="inlineStr"/>
       <c r="AG5" s="2" t="inlineStr"/>
       <c r="AH5" s="2" t="inlineStr"/>
+      <c r="AI5" s="2" t="inlineStr"/>
+      <c r="AJ5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1498,6 +1540,8 @@
       <c r="AF6" s="2" t="inlineStr"/>
       <c r="AG6" s="2" t="inlineStr"/>
       <c r="AH6" s="2" t="inlineStr"/>
+      <c r="AI6" s="2" t="inlineStr"/>
+      <c r="AJ6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -1640,6 +1684,8 @@
       <c r="AF7" s="2" t="inlineStr"/>
       <c r="AG7" s="2" t="inlineStr"/>
       <c r="AH7" s="2" t="inlineStr"/>
+      <c r="AI7" s="2" t="inlineStr"/>
+      <c r="AJ7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -1794,9 +1840,11 @@
       <c r="AF8" s="2" t="inlineStr"/>
       <c r="AG8" s="2" t="inlineStr"/>
       <c r="AH8" s="2" t="inlineStr"/>
+      <c r="AI8" s="2" t="inlineStr"/>
+      <c r="AJ8" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3:W8" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>
@@ -1842,7 +1890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1879,6 +1927,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2052,6 +2102,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2222,6 +2282,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -2346,9 +2416,11 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>
@@ -2394,7 +2466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2431,6 +2503,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2604,6 +2678,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -2774,6 +2858,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -2944,9 +3038,11 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>
@@ -2992,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3029,6 +3125,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3202,6 +3300,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -3372,6 +3480,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -3519,9 +3637,11 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>
@@ -3567,7 +3687,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3604,6 +3724,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3777,6 +3899,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -3947,6 +4079,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -4091,9 +4233,11 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>
@@ -4139,7 +4283,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4176,6 +4320,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4349,6 +4495,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -4519,6 +4675,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -4663,9 +4829,11 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>
@@ -4711,7 +4879,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH3"/>
+  <dimension ref="A1:AJ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -4748,6 +4916,8 @@
     <col width="26" customWidth="1" min="32" max="32"/>
     <col width="44" customWidth="1" min="33" max="33"/>
     <col width="18" customWidth="1" min="34" max="34"/>
+    <col width="18" customWidth="1" min="35" max="35"/>
+    <col width="18" customWidth="1" min="36" max="36"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -4921,6 +5091,16 @@
           <t>Reviewer Confidence</t>
         </is>
       </c>
+      <c r="AI1" s="3" t="inlineStr">
+        <is>
+          <t>Reviewer ID</t>
+        </is>
+      </c>
+      <c r="AJ1" s="3" t="inlineStr">
+        <is>
+          <t>Review Round</t>
+        </is>
+      </c>
     </row>
     <row r="2" hidden="1">
       <c r="A2" s="4" t="inlineStr">
@@ -5091,6 +5271,16 @@
       <c r="AH2" s="4" t="inlineStr">
         <is>
           <t>reviewer_confidence</t>
+        </is>
+      </c>
+      <c r="AI2" s="4" t="inlineStr">
+        <is>
+          <t>reviewer_id</t>
+        </is>
+      </c>
+      <c r="AJ2" s="4" t="inlineStr">
+        <is>
+          <t>review_round</t>
         </is>
       </c>
     </row>
@@ -5247,9 +5437,11 @@
       <c r="AF3" s="2" t="inlineStr"/>
       <c r="AG3" s="2" t="inlineStr"/>
       <c r="AH3" s="2" t="inlineStr"/>
+      <c r="AI3" s="2" t="inlineStr"/>
+      <c r="AJ3" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A2:AH2"/>
+  <autoFilter ref="A2:AJ2"/>
   <dataValidations count="11">
     <dataValidation sqref="W3" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid review code" error="Please choose one of the allowed review codes." promptTitle="Structured review" prompt="Use the dropdown value so the review can be summarized." type="list">
       <formula1>"yes,partial,no"</formula1>

--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -466,7 +466,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
@@ -531,14 +531,21 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>8. This workbook reviews case/source quality only. It is not an AI-response blind review and should not be used to score condition quality.</t>
+          <t>8. reviewer_id should be coach_A / coach_B / ai_reviewer_1; review_round should be calibration / round1 / adjudication.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>9. context_ai_reply / prior_ai_scaffold are only for checking whether the student reply follows the previous scaffold, not for judging that AI reply's quality.</t>
+          <t>9. This workbook reviews case/source quality only. It is not an AI-response blind review and should not be used to score condition quality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>10. context_ai_reply / prior_ai_scaffold are only for checking whether the student reply follows the previous scaffold, not for judging that AI reply's quality.</t>
         </is>
       </c>
     </row>

--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -1112,17 +1112,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>clarify</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>一个来源应该是已经处理完前面部分后的结果。</t>
+          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>一个来源应该是已经处理完前面部分后的结果。</t>
+          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -1234,14 +1234,14 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>回复引导学生列出当前一步可由哪些更小子问题产生。
-回复让学生先分析一个选择分支或一个前驱来源。
+          <t>回复先请学生把“已处理完前面部分”具体化成一个前驱来源。
+回复让学生用题面动作或选择说出当前量从哪里来。
 回复不直接写完整递推式。</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>Dialogue-state v3 draft. 请复核 followability=F1、expected_tutor_move=advance 与目标 missing bridge 是否一致。</t>
+          <t>Dialogue-state v3 draft. 请复核 followability=F2、expected_tutor_move=clarify 与目标 missing bridge 是否一致。</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr"/>
@@ -1339,17 +1339,17 @@
       <c r="M5" s="2" t="inlineStr">
         <is>
           <t>学生：顺序总写反。
-AI：先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+AI：先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断一次更新时，旧值会不会被本轮刚算出的新值覆盖或复用。</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断一次更新时，旧值会不会被本轮刚算出的新值覆盖或复用。</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断一次更新时，旧值会不会被本轮刚算出的新值覆盖或复用。</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1369,7 +1369,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>缺少把循环不变量、已处理范围和更新方向对应起来的关系。</t>
+          <t>缺少把循环方向、上一轮旧值和本轮新值复用风险对应起来的关系。</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -1381,9 +1381,9 @@
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
-回复用一个很小范围检查边界或顺序含义。
-回复不直接给完整模板或边界更新公式。</t>
+          <t>回复让学生先说清一次更新时哪些旧值必须来自上一轮或上一状态。
+回复用一个很小容量范围检查循环方向是否会复用本轮新值。
+回复不直接给完整背包模板或循环方向结论。</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1619,30 +1619,30 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
           <t>学生：题面编号、循环范围和数组大小总对不上，我不知道该先用哪个最小样例来检查。 我看样例能跟上，但换成自己写就不知道该先确认哪一步。 我现在不知道该先看思路还是先看代码，所以越写越乱。
-AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先拿最小样例核对一个边界、初值或变量范围。
+AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先拿一个字符或空格，核对它应该对应几次按键。
 学生：我能说出一点，但还是不知道它怎么落到这题里。
-AI：好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
+AI：好，我们就停在这个局部。你先回答一个更小的问题：你先拿一个字符或空格，核对它应该对应几次按键。</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿一个字符或空格，核对它应该对应几次按键。</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿一个字符或空格，核对它应该对应几次按键。</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1657,7 +1657,7 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>缺少把题面范围、数组下标、初始可达状态和变量类型对应起来的实现边界桥。</t>
+          <t>缺少把题面中的字符/空格映射到对应按键次数，并据此逐字符累加的实现桥。</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
@@ -1669,9 +1669,9 @@
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>回复让学生先用最小样例核对一个下标、初始值或类型范围。
-回复把注意力放在一个实现边界上。
-回复不直接给完整代码补丁。</t>
+          <t>回复让学生先用一个字符或空格核对对应的按键次数。
+回复把注意力放在字符到次数的局部映射上。
+回复不直接给完整代码补丁或整张字符映射表。</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -2901,17 +2901,17 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>F1</t>
+          <t>F2</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>advance</t>
+          <t>clarify</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>一个来源应该是已经处理完前面部分后的结果。</t>
+          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>一个来源应该是已经处理完前面部分后的结果。</t>
+          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -3023,14 +3023,14 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>回复引导学生列出当前一步可由哪些更小子问题产生。
-回复让学生先分析一个选择分支或一个前驱来源。
+          <t>回复先请学生把“已处理完前面部分”具体化成一个前驱来源。
+回复让学生用题面动作或选择说出当前量从哪里来。
 回复不直接写完整递推式。</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
         <is>
-          <t>Dialogue-state v3 draft. 请复核 followability=F1、expected_tutor_move=advance 与目标 missing bridge 是否一致。</t>
+          <t>Dialogue-state v3 draft. 请复核 followability=F2、expected_tutor_move=clarify 与目标 missing bridge 是否一致。</t>
         </is>
       </c>
       <c r="W3" s="2" t="inlineStr"/>
@@ -3580,17 +3580,17 @@
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>学生：顺序总写反。
-AI：先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+AI：先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断一次更新时，旧值会不会被本轮刚算出的新值覆盖或复用。</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断一次更新时，旧值会不会被本轮刚算出的新值覆盖或复用。</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断更新后哪一边还可能包含答案，或者哪个旧值不能被覆盖。</t>
+          <t>先别急着要完整做法。围绕《[NOIP 2006 普及组] 开心的金明》，我们只拆当前一小步：你先判断一次更新时，旧值会不会被本轮刚算出的新值覆盖或复用。</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>缺少把循环不变量、已处理范围和更新方向对应起来的关系。</t>
+          <t>缺少把循环方向、上一轮旧值和本轮新值复用风险对应起来的关系。</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -3622,9 +3622,9 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>回复让学生先说清更新前后哪一段仍可能包含答案或仍可被复用。
-回复用一个很小范围检查边界或顺序含义。
-回复不直接给完整模板或边界更新公式。</t>
+          <t>回复让学生先说清一次更新时哪些旧值必须来自上一轮或上一状态。
+回复用一个很小容量范围检查循环方向是否会复用本轮新值。
+回复不直接给完整背包模板或循环方向结论。</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">
@@ -4764,30 +4764,30 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
           <t>学生：题面编号、循环范围和数组大小总对不上，我不知道该先用哪个最小样例来检查。 我看样例能跟上，但换成自己写就不知道该先确认哪一步。 我现在不知道该先看思路还是先看代码，所以越写越乱。
-AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先拿最小样例核对一个边界、初值或变量范围。
+AI：先别急着要完整做法。围绕《手机》，我们只拆当前一小步：你先拿一个字符或空格，核对它应该对应几次按键。
 学生：我能说出一点，但还是不知道它怎么落到这题里。
-AI：好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
+AI：好，我们就停在这个局部。你先回答一个更小的问题：你先拿一个字符或空格，核对它应该对应几次按键。</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿一个字符或空格，核对它应该对应几次按键。</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿最小样例核对一个边界、初值或变量范围。</t>
+          <t>好，我们就停在这个局部。你先回答一个更小的问题：你先拿一个字符或空格，核对它应该对应几次按键。</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？输入范围我也没对上。 如果可以的话，能不能先用这题里的一个字符解释该检查哪个下标或输入边界？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>缺少把题面范围、数组下标、初始可达状态和变量类型对应起来的实现边界桥。</t>
+          <t>缺少把题面中的字符/空格映射到对应按键次数，并据此逐字符累加的实现桥。</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
@@ -4814,9 +4814,9 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>回复让学生先用最小样例核对一个下标、初始值或类型范围。
-回复把注意力放在一个实现边界上。
-回复不直接给完整代码补丁。</t>
+          <t>回复让学生先用一个字符或空格核对对应的按键次数。
+回复把注意力放在字符到次数的局部映射上。
+回复不直接给完整代码补丁或整张字符映射表。</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">

--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -1190,7 +1190,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
+          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
+          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2979,7 +2979,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
+          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是已经处理完前面部分后的结果，可我还没说清它对应哪个题目动作。</t>
+          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">

--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>followup_after_partial_answer</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
+          <t>我能想到一个来源，但没对应到具体题面动作。</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
@@ -1211,15 +1211,19 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
+          <t>我能想到一个来源，但没对应到具体题面动作。</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr"/>
+          <t>我能想到一个来源</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>学生方向接近，但没有说清分支或条件。</t>
+        </is>
+      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
           <t>缺少根据题目允许的动作、选择或依赖关系反推转移来源。</t>
@@ -1234,7 +1238,7 @@
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>回复先请学生把“已处理完前面部分”具体化成一个前驱来源。
+          <t>回复先请学生把“前面某个状态”具体化成一个前驱来源。
 回复让学生用题面动作或选择说出当前量从哪里来。
 回复不直接写完整递推式。</t>
         </is>
@@ -1619,7 +1623,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我这里卡在最基础的地方：空格算几下，字母又怎么数？能先拿一个字母带我核一下吗？ 我先想把一个字母和一个空格的按键次数算对，不然循环写了也不知道对不对；先别给整段代码。</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -1642,12 +1646,12 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我这里卡在最基础的地方：空格算几下，字母又怎么数？能先拿一个字母带我核一下吗？ 我先想把一个字母和一个空格的按键次数算对，不然循环写了也不知道对不对；先别给整段代码。</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里</t>
+          <t>我这里卡在最基础</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
@@ -1657,21 +1661,21 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>缺少把题面中的字符/空格映射到对应按键次数，并据此逐字符累加的实现桥。</t>
+          <t>缺少把题面中的单个字符（字母或空格）映射到按键次数，并把输入逐字符累计的实现桥。</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
           <t>no_complete_code_patch
 no_full_solution
-no_direct_current_bridge</t>
+no_full_keypress_mapping_table</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>回复让学生先用一个字符或空格核对对应的按键次数。
-回复把注意力放在字符到次数的局部映射上。
-回复不直接给完整代码补丁或整张字符映射表。</t>
+          <t>回复先选一个字符或空格，让学生根据题面数出对应按键次数。
+回复只建立“单字符映射 -&gt; 逐字符累计”的局部关系。
+回复不直接给完整代码、整张字符映射表或整题总做法。</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -2896,7 +2900,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>followup_after_correct_short_answer</t>
+          <t>followup_after_partial_answer</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -2979,7 +2983,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
+          <t>我能想到一个来源，但没对应到具体题面动作。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -3000,15 +3004,19 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>一个来源大概是前面结果，但我还没说清对应哪个动作。</t>
+          <t>我能想到一个来源，但没对应到具体题面动作。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>来源</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
+          <t>我能想到一个来源</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>学生方向接近，但没有说清分支或条件。</t>
+        </is>
+      </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
           <t>缺少根据题目允许的动作、选择或依赖关系反推转移来源。</t>
@@ -3023,7 +3031,7 @@
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>回复先请学生把“已处理完前面部分”具体化成一个前驱来源。
+          <t>回复先请学生把“前面某个状态”具体化成一个前驱来源。
 回复让学生用题面动作或选择说出当前量从哪里来。
 回复不直接写完整递推式。</t>
         </is>
@@ -4764,7 +4772,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我这里卡在最基础的地方：空格算几下，字母又怎么数？能先拿一个字母带我核一下吗？ 我先想把一个字母和一个空格的按键次数算对，不然循环写了也不知道对不对；先别给整段代码。</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr">
@@ -4787,12 +4795,12 @@
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里空格和字母要怎么对应到次数？ 如果可以的话，能不能先用这题里的一个字符或空格解释它该算几次按键？ 我希望先确认这个小关系，因为一旦这里错了，后面写代码就会一直靠猜。</t>
+          <t>我这里卡在最基础的地方：空格算几下，字母又怎么数？能先拿一个字母带我核一下吗？ 我先想把一个字母和一个空格的按键次数算对，不然循环写了也不知道对不对；先别给整段代码。</t>
         </is>
       </c>
       <c r="Q3" s="2" t="inlineStr">
         <is>
-          <t>我有点懵，这题里</t>
+          <t>我这里卡在最基础</t>
         </is>
       </c>
       <c r="R3" s="2" t="inlineStr">
@@ -4802,21 +4810,21 @@
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>缺少把题面中的字符/空格映射到对应按键次数，并据此逐字符累加的实现桥。</t>
+          <t>缺少把题面中的单个字符（字母或空格）映射到按键次数，并把输入逐字符累计的实现桥。</t>
         </is>
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
           <t>no_complete_code_patch
 no_full_solution
-no_direct_current_bridge</t>
+no_full_keypress_mapping_table</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
         <is>
-          <t>回复让学生先用一个字符或空格核对对应的按键次数。
-回复把注意力放在字符到次数的局部映射上。
-回复不直接给完整代码补丁或整张字符映射表。</t>
+          <t>回复先选一个字符或空格，让学生根据题面数出对应按键次数。
+回复只建立“单字符映射 -&gt; 逐字符累计”的局部关系。
+回复不直接给完整代码、整张字符映射表或整题总做法。</t>
         </is>
       </c>
       <c r="V3" s="2" t="inlineStr">

--- a/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
+++ b/agent_learning/03_noi_agent/docs/research/dialogue_state_v3_case_review_calibration_6.en.xlsx
@@ -1057,9 +1057,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_exact_state_definition
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not give the exact full state/variable definition
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -1231,9 +1231,9 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>no_exact_recurrence
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not write the full recurrence or transition equation
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -1378,9 +1378,9 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>no_exact_boundary_update_rule
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not give the exact boundary update or loop-order rule
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -1522,9 +1522,9 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>no_complete_model_mapping
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not give the full modeling mapping
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1666,9 +1666,9 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>no_complete_code_patch
-no_full_solution
-no_full_keypress_mapping_table</t>
+          <t>Do not rewrite the full code for the student
+Do not provide the full solution
+Do not provide the full keypress mapping table</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1822,9 +1822,9 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>no_full_solution
-no_full_code
-no_direct_answer_confirmation</t>
+          <t>Do not provide the full solution
+Do not provide full code
+Do not directly confirm the full answer, algorithm, or solution path</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2398,9 +2398,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_exact_state_definition
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not give the exact full state/variable definition
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -3024,9 +3024,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_exact_recurrence
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not write the full recurrence or transition equation
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -3623,9 +3623,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_exact_boundary_update_rule
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not give the exact boundary update or loop-order rule
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -4219,9 +4219,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_complete_model_mapping
-no_full_solution
-no_direct_current_bridge</t>
+          <t>Do not give the full modeling mapping
+Do not provide the full solution
+Do not directly complete the student's current missing bridge</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -4815,9 +4815,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_complete_code_patch
-no_full_solution
-no_full_keypress_mapping_table</t>
+          <t>Do not rewrite the full code for the student
+Do not provide the full solution
+Do not provide the full keypress mapping table</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
@@ -5423,9 +5423,9 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>no_full_solution
-no_full_code
-no_direct_answer_confirmation</t>
+          <t>Do not provide the full solution
+Do not provide full code
+Do not directly confirm the full answer, algorithm, or solution path</t>
         </is>
       </c>
       <c r="U3" s="2" t="inlineStr">
